--- a/tests/fixtures/annuaire-exemple.xlsx
+++ b/tests/fixtures/annuaire-exemple.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Annuaire" sheetId="1" r:id="rId1"/>
-    <sheet name="Historique" sheetId="2" r:id="rId2"/>
+    <sheet name="Entités" sheetId="1" r:id="rId1"/>
+    <sheet name="AliasParSite" sheetId="2" r:id="rId2"/>
+    <sheet name="Historique" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,290 +399,251 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:F11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>ID entité</v>
+      </c>
+      <c r="B1" t="str">
         <v>Type</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Nom réel</v>
       </c>
-      <c r="C1" t="str">
-        <v>Alias actif</v>
-      </c>
       <c r="D1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="E1" t="str">
         <v>Format</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Site</v>
       </c>
       <c r="F1" t="str">
         <v>Créé le</v>
       </c>
-      <c r="G1" t="str">
-        <v>Expire le</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>ent-01</v>
+      </c>
+      <c r="B2" t="str">
         <v>PER</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>Pierre Dupont</v>
       </c>
-      <c r="C2" t="str">
-        <v>PDT-2</v>
-      </c>
       <c r="D2" t="str">
+        <v>pierre.dupont@example.test</v>
+      </c>
+      <c r="E2" t="str">
         <v>court</v>
-      </c>
-      <c r="E2" t="str">
-        <v>chat.openai.com</v>
       </c>
       <c r="F2" t="str">
         <v>2025-10-01</v>
       </c>
-      <c r="G2" t="str">
-        <v>2027-01-01</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>ent-02</v>
+      </c>
+      <c r="B3" t="str">
         <v>PER</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>Paul Dumont</v>
       </c>
-      <c r="C3" t="str">
-        <v>PDT-3</v>
-      </c>
       <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
         <v>court</v>
-      </c>
-      <c r="E3" t="str">
-        <v>chat.openai.com</v>
       </c>
       <c r="F3" t="str">
         <v>2026-05-01</v>
       </c>
-      <c r="G3" t="str">
-        <v>2027-05-01</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>ent-03</v>
+      </c>
+      <c r="B4" t="str">
         <v>PER</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>Marie Lefebvre</v>
       </c>
-      <c r="C4" t="str">
-        <v>MALE</v>
-      </c>
       <c r="D4" t="str">
+        <v>marie.lefebvre@example.test</v>
+      </c>
+      <c r="E4" t="str">
         <v>etendu</v>
-      </c>
-      <c r="E4" t="str">
-        <v>claude.ai</v>
       </c>
       <c r="F4" t="str">
         <v>2026-02-15</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>ent-04</v>
+      </c>
+      <c r="B5" t="str">
         <v>PER</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>Jean Test</v>
       </c>
-      <c r="C5" t="str">
-        <v>X7K2Q</v>
-      </c>
       <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
         <v>opaque</v>
-      </c>
-      <c r="E5" t="str">
-        <v>file://tests/fixtures/mock-ai-site/</v>
       </c>
       <c r="F5" t="str">
         <v>2026-07-15</v>
       </c>
-      <c r="G5" t="str">
-        <v>2026-07-22</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>ent-05</v>
+      </c>
+      <c r="B6" t="str">
         <v>ORG</v>
       </c>
-      <c r="B6" t="str">
+      <c r="C6" t="str">
         <v>Acme Corporation</v>
       </c>
-      <c r="C6" t="str">
-        <v>ACN</v>
-      </c>
       <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
         <v>court</v>
-      </c>
-      <c r="E6" t="str">
-        <v>chat.openai.com</v>
       </c>
       <c r="F6" t="str">
         <v>2026-03-01</v>
       </c>
-      <c r="G6" t="str">
-        <v>2027-03-01</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>ent-06</v>
+      </c>
+      <c r="B7" t="str">
         <v>ORG</v>
       </c>
-      <c r="B7" t="str">
+      <c r="C7" t="str">
         <v>Beta Industries</v>
       </c>
-      <c r="C7" t="str">
-        <v>BEIN</v>
-      </c>
       <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
         <v>etendu</v>
-      </c>
-      <c r="E7" t="str">
-        <v>claude.ai</v>
       </c>
       <c r="F7" t="str">
         <v>2026-01-10</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>ent-07</v>
+      </c>
+      <c r="B8" t="str">
         <v>LIE</v>
       </c>
-      <c r="B8" t="str">
+      <c r="C8" t="str">
         <v>Paris</v>
       </c>
-      <c r="C8" t="str">
-        <v>PAIS</v>
-      </c>
       <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
         <v>court</v>
-      </c>
-      <c r="E8" t="str">
-        <v>chat.openai.com</v>
       </c>
       <c r="F8" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="G8" t="str">
-        <v>2027-04-01</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>ent-08</v>
+      </c>
+      <c r="B9" t="str">
         <v>LIE</v>
       </c>
-      <c r="B9" t="str">
+      <c r="C9" t="str">
         <v>New York</v>
       </c>
-      <c r="C9" t="str">
-        <v>NYK</v>
-      </c>
       <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
         <v>court</v>
-      </c>
-      <c r="E9" t="str">
-        <v>claude.ai</v>
       </c>
       <c r="F9" t="str">
         <v>2026-05-20</v>
       </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>ent-09</v>
+      </c>
+      <c r="B10" t="str">
         <v>PRJ</v>
       </c>
-      <c r="B10" t="str">
+      <c r="C10" t="str">
         <v>Projet Aurore</v>
       </c>
-      <c r="C10" t="str">
-        <v>PAE</v>
-      </c>
       <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
         <v>court</v>
-      </c>
-      <c r="E10" t="str">
-        <v>chat.openai.com</v>
       </c>
       <c r="F10" t="str">
         <v>2026-06-01</v>
       </c>
-      <c r="G10" t="str">
-        <v>2027-06-01</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>ent-10</v>
+      </c>
+      <c r="B11" t="str">
         <v>PRJ</v>
       </c>
-      <c r="B11" t="str">
+      <c r="C11" t="str">
         <v>Migration Phoenix</v>
       </c>
-      <c r="C11" t="str">
-        <v>MIPH</v>
-      </c>
       <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
         <v>etendu</v>
-      </c>
-      <c r="E11" t="str">
-        <v>file://tests/fixtures/mock-ai-site/</v>
       </c>
       <c r="F11" t="str">
         <v>2026-07-18</v>
       </c>
-      <c r="G11" t="str">
-        <v>2026-07-25</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:D12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ID entité</v>
       </c>
       <c r="B1" t="str">
-        <v>Type</v>
+        <v>Site</v>
       </c>
       <c r="C1" t="str">
-        <v>Nom réel</v>
+        <v>Alias actif</v>
       </c>
       <c r="D1" t="str">
-        <v>Alias</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Attribué le</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Expiré le</v>
+        <v>Expire le</v>
       </c>
     </row>
     <row r="2">
@@ -689,19 +651,13 @@
         <v>ent-01</v>
       </c>
       <c r="B2" t="str">
-        <v>PER</v>
+        <v>chat.openai.com</v>
       </c>
       <c r="C2" t="str">
-        <v>Pierre Dupont</v>
+        <v>PDT-2</v>
       </c>
       <c r="D2" t="str">
-        <v>PDT</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-01-01</v>
+        <v>2027-01-01</v>
       </c>
     </row>
     <row r="3">
@@ -709,19 +665,13 @@
         <v>ent-01</v>
       </c>
       <c r="B3" t="str">
-        <v>PER</v>
+        <v>claude.ai</v>
       </c>
       <c r="C3" t="str">
-        <v>Pierre Dupont</v>
+        <v>PDT</v>
       </c>
       <c r="D3" t="str">
-        <v>PDT-2</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2027-01-01</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -729,18 +679,12 @@
         <v>ent-02</v>
       </c>
       <c r="B4" t="str">
-        <v>PER</v>
+        <v>chat.openai.com</v>
       </c>
       <c r="C4" t="str">
-        <v>Paul Dumont</v>
+        <v>PDT-3</v>
       </c>
       <c r="D4" t="str">
-        <v>PDT-3</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="F4" t="str">
         <v>2027-05-01</v>
       </c>
     </row>
@@ -749,18 +693,12 @@
         <v>ent-03</v>
       </c>
       <c r="B5" t="str">
-        <v>PER</v>
+        <v>claude.ai</v>
       </c>
       <c r="C5" t="str">
-        <v>Marie Lefebvre</v>
+        <v>MALE</v>
       </c>
       <c r="D5" t="str">
-        <v>MALE</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="F5" t="str">
         <v/>
       </c>
     </row>
@@ -769,18 +707,12 @@
         <v>ent-04</v>
       </c>
       <c r="B6" t="str">
-        <v>PER</v>
+        <v>file://tests/fixtures/mock-ai-site/</v>
       </c>
       <c r="C6" t="str">
-        <v>Jean Test</v>
+        <v>X7K2Q</v>
       </c>
       <c r="D6" t="str">
-        <v>X7K2Q</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-07-15</v>
-      </c>
-      <c r="F6" t="str">
         <v>2026-07-22</v>
       </c>
     </row>
@@ -789,18 +721,12 @@
         <v>ent-05</v>
       </c>
       <c r="B7" t="str">
-        <v>ORG</v>
+        <v>chat.openai.com</v>
       </c>
       <c r="C7" t="str">
-        <v>Acme Corporation</v>
+        <v>ACN</v>
       </c>
       <c r="D7" t="str">
-        <v>ACN</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="F7" t="str">
         <v>2027-03-01</v>
       </c>
     </row>
@@ -809,18 +735,12 @@
         <v>ent-06</v>
       </c>
       <c r="B8" t="str">
-        <v>ORG</v>
+        <v>claude.ai</v>
       </c>
       <c r="C8" t="str">
-        <v>Beta Industries</v>
+        <v>BEIN</v>
       </c>
       <c r="D8" t="str">
-        <v>BEIN</v>
-      </c>
-      <c r="E8" t="str">
-        <v>2026-01-10</v>
-      </c>
-      <c r="F8" t="str">
         <v/>
       </c>
     </row>
@@ -829,18 +749,12 @@
         <v>ent-07</v>
       </c>
       <c r="B9" t="str">
-        <v>LIE</v>
+        <v>chat.openai.com</v>
       </c>
       <c r="C9" t="str">
-        <v>Paris</v>
+        <v>PAIS</v>
       </c>
       <c r="D9" t="str">
-        <v>PAIS</v>
-      </c>
-      <c r="E9" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="F9" t="str">
         <v>2027-04-01</v>
       </c>
     </row>
@@ -849,18 +763,12 @@
         <v>ent-08</v>
       </c>
       <c r="B10" t="str">
-        <v>LIE</v>
+        <v>claude.ai</v>
       </c>
       <c r="C10" t="str">
-        <v>New York</v>
+        <v>NYK</v>
       </c>
       <c r="D10" t="str">
-        <v>NYK</v>
-      </c>
-      <c r="E10" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="F10" t="str">
         <v/>
       </c>
     </row>
@@ -869,18 +777,12 @@
         <v>ent-09</v>
       </c>
       <c r="B11" t="str">
-        <v>PRJ</v>
+        <v>chat.openai.com</v>
       </c>
       <c r="C11" t="str">
-        <v>Projet Aurore</v>
+        <v>PAE</v>
       </c>
       <c r="D11" t="str">
-        <v>PAE</v>
-      </c>
-      <c r="E11" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="F11" t="str">
         <v>2027-06-01</v>
       </c>
     </row>
@@ -889,24 +791,250 @@
         <v>ent-10</v>
       </c>
       <c r="B12" t="str">
-        <v>PRJ</v>
+        <v>file://tests/fixtures/mock-ai-site/</v>
       </c>
       <c r="C12" t="str">
-        <v>Migration Phoenix</v>
+        <v>MIPH</v>
       </c>
       <c r="D12" t="str">
-        <v>MIPH</v>
-      </c>
-      <c r="E12" t="str">
-        <v>2026-07-18</v>
-      </c>
-      <c r="F12" t="str">
         <v>2026-07-25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID entité</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Site</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Alias</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Attribué le</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Expiré le</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ent-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>chat.openai.com</v>
+      </c>
+      <c r="C2" t="str">
+        <v>PDT</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-01-01</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ent-01</v>
+      </c>
+      <c r="B3" t="str">
+        <v>chat.openai.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PDT-2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2027-01-01</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ent-01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>claude.ai</v>
+      </c>
+      <c r="C4" t="str">
+        <v>PDT</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ent-02</v>
+      </c>
+      <c r="B5" t="str">
+        <v>chat.openai.com</v>
+      </c>
+      <c r="C5" t="str">
+        <v>PDT-3</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2027-05-01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ent-03</v>
+      </c>
+      <c r="B6" t="str">
+        <v>claude.ai</v>
+      </c>
+      <c r="C6" t="str">
+        <v>MALE</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ent-04</v>
+      </c>
+      <c r="B7" t="str">
+        <v>file://tests/fixtures/mock-ai-site/</v>
+      </c>
+      <c r="C7" t="str">
+        <v>X7K2Q</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2026-07-22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ent-05</v>
+      </c>
+      <c r="B8" t="str">
+        <v>chat.openai.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ACN</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2027-03-01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ent-06</v>
+      </c>
+      <c r="B9" t="str">
+        <v>claude.ai</v>
+      </c>
+      <c r="C9" t="str">
+        <v>BEIN</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ent-07</v>
+      </c>
+      <c r="B10" t="str">
+        <v>chat.openai.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>PAIS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2027-04-01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ent-08</v>
+      </c>
+      <c r="B11" t="str">
+        <v>claude.ai</v>
+      </c>
+      <c r="C11" t="str">
+        <v>NYK</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ent-09</v>
+      </c>
+      <c r="B12" t="str">
+        <v>chat.openai.com</v>
+      </c>
+      <c r="C12" t="str">
+        <v>PAE</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2027-06-01</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ent-10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>file://tests/fixtures/mock-ai-site/</v>
+      </c>
+      <c r="C13" t="str">
+        <v>MIPH</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-07-18</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-07-25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
   </ignoredErrors>
 </worksheet>
 </file>